--- a/data/hotel.xlsx
+++ b/data/hotel.xlsx
@@ -6,6 +6,7 @@
     <sheet name="room_types" sheetId="2" r:id="rId2"/>
     <sheet name="bookings" sheetId="3" r:id="rId3"/>
     <sheet name="users" sheetId="4" r:id="rId4"/>
+    <sheet name="audit_log" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -933,6 +934,108 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0008</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>101</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">สมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">081-234-5678</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">somchai@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-20</t>
+        </is>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>7250</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">checkin</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:00:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0009</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>102</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">สมหญิง ใจร้าย</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0812345678</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">som@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-16</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1200</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wait</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 15:46:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -980,7 +1083,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin123</t>
+          <t xml:space="preserve">sha256$95f3333aad80cbe6$5ad25f31447fe3cebb66038b9e5882d7305b18fa7a62168e8e176ad4ecac5e99</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1012,7 +1115,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">staff123</t>
+          <t xml:space="preserve">sha256$92cf4439593c8044$ecd353902110919fe02223af5f8533ffe3ae0855da4b4d53143c14da48cac3fd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1044,7 +1147,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">guest123</t>
+          <t xml:space="preserve">sha256$c50a708acf46b3c0$e35bbca995688c21ec4a9645b5293ae7a5b665ae5461ad2b7fbc3c27ea40262e</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1071,12 +1174,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">newguest</t>
+          <t xml:space="preserve">สมหญิง</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pass123</t>
+          <t xml:space="preserve">sha256$b3a9eb1cee617bcc$2c1507a8690ad238bafb11b5956345165806a38ac2907e19fa05ef2d365f98fa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1086,45 +1189,875 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test User</t>
+          <t xml:space="preserve">สมหญิง ใจร้าย</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">089-999-8888</t>
+          <t xml:space="preserve">0812345678</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">test@example.com</t>
+          <t xml:space="preserve">som@gmail.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">log_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_user</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_role</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">action_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">target_entity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:19:37</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:19:37</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:19:47</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User teststaff99</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Test Staff 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:19:47</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User teststaff99</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Promoted Admin 99, Phone: 089-999-8888, Email: promoted@hotel.com, Password reset to new Salted SHA-256</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PPP</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1234</v>
+          <t xml:space="preserve">LOG-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:21:01</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:21:01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:27:29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:27:29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:46:54</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:46:54</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:57:58</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 13:57:58</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:00:56</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">สมชาย ใจดี</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t xml:space="preserve">guest</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PPP</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>1234</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PP@gmail.com</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOOKING_CREATED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Booking B0008</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Room 101, 2026-09-15 -&gt; 2026-09-20 (5 nights, 7250 THB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:28:20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:28:20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:32:10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:32:10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:34:16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:34:16</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:44:53</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 14:44:53</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-15 15:46:41</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User สมหญิง</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: guest, Name: สมหญิง ใจร้าย</t>
         </is>
       </c>
     </row>

--- a/data/hotel.xlsx
+++ b/data/hotel.xlsx
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sha256$95f3333aad80cbe6$5ad25f31447fe3cebb66038b9e5882d7305b18fa7a62168e8e176ad4ecac5e99</t>
+          <t xml:space="preserve">sha256$e1e1349ad67e1872$13ff24383ca0f83038ecf1821f42b37baa63c0aa9b8c11c444c21cc2dc442ed4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sha256$92cf4439593c8044$ecd353902110919fe02223af5f8533ffe3ae0855da4b4d53143c14da48cac3fd</t>
+          <t xml:space="preserve">sha256$9a0c3439877687f6$9bf5d7a9ff40717eaeff4235721f1ce27e1e27fb3bf2d5a4d573891b6a85cfdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sha256$c50a708acf46b3c0$e35bbca995688c21ec4a9645b5293ae7a5b665ae5461ad2b7fbc3c27ea40262e</t>
+          <t xml:space="preserve">sha256$841d9a9ab8435256$60e27248942d3dd07b8aabf12731a34a257eb14022a1913ddc2285214fcf5daa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1168,38 +1168,6 @@
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">somchai@gmail.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">สมหญิง</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sha256$b3a9eb1cee617bcc$2c1507a8690ad238bafb11b5956345165806a38ac2907e19fa05ef2d365f98fa</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guest</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">สมหญิง ใจร้าย</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0812345678</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">som@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2061,6 +2029,80 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 03:05:38</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_CREATED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff, Name: Manager Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOG-0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 03:05:38</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USER_UPDATED</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User newmanager</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role: staff-&gt;admin, Name: Manager Promoted, Phone: 081-888-8888, Email: mgr2@test.com, Password reset to new Salted SHA-256</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>